--- a/sheets/조재수대금교본/검수/뱃노래.xlsx
+++ b/sheets/조재수대금교본/검수/뱃노래.xlsx
@@ -2438,7 +2438,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -2546,9 +2546,7 @@
       <c r="I5" s="23"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z
-–
-Z</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K5" s="23"/>
@@ -2640,13 +2638,13 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∽</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="E7" s="22"/>
@@ -2660,21 +2658,20 @@
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∽</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I7" s="22"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–
-Z</t>
+–</t>
         </is>
       </c>
       <c r="K7" s="22"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∽</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M7" s="22"/>
@@ -2785,11 +2782,7 @@
         </is>
       </c>
       <c r="E10" s="24"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="24"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
@@ -2799,11 +2792,7 @@
         </is>
       </c>
       <c r="I10" s="24"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="24"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
@@ -2813,17 +2802,9 @@
         </is>
       </c>
       <c r="M10" s="24"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="24"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/뱃노래.xlsx
+++ b/sheets/조재수대금교본/검수/뱃노래.xlsx
@@ -2438,7 +2438,7 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -2546,7 +2546,9 @@
       <c r="I5" s="23"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">Z
+–
+Z</t>
         </is>
       </c>
       <c r="K5" s="23"/>
@@ -2638,13 +2640,13 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∽</t>
         </is>
       </c>
       <c r="E7" s="22"/>
@@ -2658,20 +2660,21 @@
       <c r="G7" s="22"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∽</t>
         </is>
       </c>
       <c r="I7" s="22"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–
+Z</t>
         </is>
       </c>
       <c r="K7" s="22"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∽</t>
         </is>
       </c>
       <c r="M7" s="22"/>

--- a/sheets/조재수대금교본/검수/뱃노래.xlsx
+++ b/sheets/조재수대금교본/검수/뱃노래.xlsx
@@ -2358,28 +2358,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="57.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="129.38" customHeight="true">
+    <row r="3" ht="144.08" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="129.38" customHeight="true">
+    <row r="4" ht="144.08" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="129.38" customHeight="true">
+    <row r="5" ht="144.08" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="Q5" s="23"/>
     </row>
-    <row r="6" ht="129.38" customHeight="true">
+    <row r="6" ht="144.08" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="Q6" s="24"/>
     </row>
-    <row r="7" ht="129.38" customHeight="true">
+    <row r="7" ht="144.08" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Q7" s="22"/>
     </row>
-    <row r="8" ht="129.38" customHeight="true">
+    <row r="8" ht="144.08" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -2730,7 +2730,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="23"/>
     </row>
-    <row r="9" ht="129.38" customHeight="true">
+    <row r="9" ht="144.08" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -2767,7 +2767,7 @@
       <c r="P9" s="21"/>
       <c r="Q9" s="23"/>
     </row>
-    <row r="10" ht="129.38" customHeight="true">
+    <row r="10" ht="144.08" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2816,6 +2816,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="69"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>